--- a/data.xlsx
+++ b/data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="133">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -233,36 +233,21 @@
     <t>安全事件类型TOP5</t>
   </si>
   <si>
-    <t>渗透框架</t>
-  </si>
-  <si>
     <t>平均处置时间（分钟）</t>
   </si>
   <si>
     <t>识别</t>
   </si>
   <si>
-    <t>木马</t>
-  </si>
-  <si>
     <t>响应</t>
   </si>
   <si>
-    <t>代理工具</t>
-  </si>
-  <si>
     <t>遏制</t>
   </si>
   <si>
-    <t>挖矿</t>
-  </si>
-  <si>
     <t>处置</t>
   </si>
   <si>
-    <t>账号安全</t>
-  </si>
-  <si>
     <t>闭环</t>
   </si>
   <si>
@@ -324,15 +309,6 @@
   </si>
   <si>
     <t>最新威胁情报数量</t>
-  </si>
-  <si>
-    <t>中国 山东省</t>
-  </si>
-  <si>
-    <t>代码注入</t>
-  </si>
-  <si>
-    <t>192.168.22.54（应用服务器）</t>
   </si>
   <si>
     <t>最新威胁影响资产数</t>
@@ -1888,7 +1864,7 @@
       </c>
       <c r="I1" s="8">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -2383,15 +2359,13 @@
       <c r="B51" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C51" s="49" t="s">
-        <v>64</v>
-      </c>
+      <c r="C51" s="49"/>
       <c r="D51" s="20"/>
       <c r="E51" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="20" t="s">
         <v>65</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>66</v>
       </c>
       <c r="G51" s="50"/>
       <c r="H51" s="18"/>
@@ -2404,13 +2378,11 @@
     </row>
     <row r="52" spans="1:14">
       <c r="B52" s="7"/>
-      <c r="C52" s="51" t="s">
-        <v>67</v>
-      </c>
+      <c r="C52" s="51"/>
       <c r="D52" s="20"/>
       <c r="E52" s="7"/>
       <c r="F52" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G52" s="50"/>
       <c r="H52" s="18"/>
@@ -2423,13 +2395,11 @@
     </row>
     <row r="53" spans="1:14">
       <c r="B53" s="7"/>
-      <c r="C53" s="51" t="s">
-        <v>69</v>
-      </c>
+      <c r="C53" s="51"/>
       <c r="D53" s="20"/>
       <c r="E53" s="7"/>
       <c r="F53" s="20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G53" s="50"/>
       <c r="H53" s="18"/>
@@ -2442,13 +2412,11 @@
     </row>
     <row r="54" spans="1:14">
       <c r="B54" s="7"/>
-      <c r="C54" s="51" t="s">
-        <v>71</v>
-      </c>
+      <c r="C54" s="51"/>
       <c r="D54" s="20"/>
       <c r="E54" s="7"/>
       <c r="F54" s="20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G54" s="50"/>
       <c r="H54" s="18"/>
@@ -2461,13 +2429,11 @@
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="7"/>
-      <c r="C55" s="51" t="s">
-        <v>73</v>
-      </c>
+      <c r="C55" s="51"/>
       <c r="D55" s="20"/>
       <c r="E55" s="7"/>
       <c r="F55" s="20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G55" s="50"/>
       <c r="H55" s="18"/>
@@ -2490,7 +2456,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -2507,10 +2473,10 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="8"/>
@@ -2527,7 +2493,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
@@ -2547,41 +2513,41 @@
     </row>
     <row r="61" ht="30" customHeight="1" spans="1:14">
       <c r="B61" s="20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D61" s="54"/>
       <c r="E61" s="44"/>
       <c r="F61" s="55" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H61" s="57"/>
       <c r="I61" s="55" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J61" s="56" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K61" s="57"/>
       <c r="L61" s="55" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M61" s="58" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N61" s="45"/>
     </row>
     <row r="62" ht="27" customHeight="1" spans="1:14">
       <c r="B62" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D62" s="20"/>
       <c r="F62" s="59"/>
@@ -2597,7 +2563,7 @@
     <row r="63" ht="27" customHeight="1" spans="1:14">
       <c r="B63" s="20"/>
       <c r="C63" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D63" s="20"/>
       <c r="F63" s="59"/>
@@ -2613,7 +2579,7 @@
     <row r="64" ht="27" customHeight="1" spans="1:14">
       <c r="B64" s="20"/>
       <c r="C64" s="9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D64" s="20"/>
       <c r="F64" s="59"/>
@@ -2628,10 +2594,10 @@
     </row>
     <row r="65" ht="27" customHeight="1" spans="2:14">
       <c r="B65" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>6</v>
@@ -2649,7 +2615,7 @@
     <row r="66" ht="27" customHeight="1" spans="2:14">
       <c r="B66" s="20"/>
       <c r="C66" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>6</v>
@@ -2666,27 +2632,18 @@
     </row>
     <row r="67" ht="27" customHeight="1" spans="2:14">
       <c r="B67" s="20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D67" s="20"/>
-      <c r="F67" t="s">
-        <v>95</v>
-      </c>
-      <c r="I67" t="s">
-        <v>96</v>
-      </c>
-      <c r="L67" t="s">
-        <v>97</v>
-      </c>
       <c r="N67" s="30"/>
     </row>
     <row r="68" ht="27" customHeight="1" spans="2:14">
       <c r="B68" s="20"/>
       <c r="C68" s="9" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D68" s="13"/>
       <c r="N68" s="30"/>
@@ -2697,7 +2654,7 @@
     </row>
     <row r="70" spans="2:14">
       <c r="B70" s="64" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C70" s="65"/>
       <c r="D70" s="65"/>
@@ -2714,7 +2671,7 @@
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="20" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="8"/>
@@ -2731,7 +2688,7 @@
     </row>
     <row r="72" spans="2:14">
       <c r="B72" s="15" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C72" s="54"/>
       <c r="D72" s="54"/>
@@ -2748,7 +2705,7 @@
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="15" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C73" s="54"/>
       <c r="D73" s="54"/>
@@ -2765,7 +2722,7 @@
     </row>
     <row r="74" spans="2:14">
       <c r="B74" s="15" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C74" s="54"/>
       <c r="D74" s="54"/>
@@ -2782,7 +2739,7 @@
     </row>
     <row r="75" spans="2:14">
       <c r="B75" s="15" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
@@ -2799,7 +2756,7 @@
     </row>
     <row r="76" spans="2:14">
       <c r="B76" s="15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
@@ -2816,7 +2773,7 @@
     </row>
     <row r="77" spans="2:14">
       <c r="B77" s="15" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -2836,34 +2793,36 @@
     </row>
     <row r="79" ht="28.8" spans="2:14">
       <c r="B79" s="20" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G79" s="44"/>
       <c r="H79" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K79" s="20"/>
       <c r="L79" s="44"/>
       <c r="M79" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="N79" s="68"/>
+        <v>105</v>
+      </c>
+      <c r="N79" s="68" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="80" spans="2:14">
       <c r="B80" s="20"/>
@@ -2872,11 +2831,11 @@
       <c r="E80" s="13"/>
       <c r="F80" s="47"/>
       <c r="H80" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="K80" s="20"/>
       <c r="N80" s="30"/>
@@ -2888,31 +2847,31 @@
       <c r="E81" s="29"/>
       <c r="F81" s="29"/>
       <c r="H81" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I81" s="70"/>
       <c r="J81" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K81" s="20"/>
       <c r="N81" s="30"/>
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="20" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="20" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="9" t="s">
@@ -2924,7 +2883,7 @@
     <row r="83" spans="2:14">
       <c r="B83" s="20"/>
       <c r="C83" s="9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
@@ -2940,7 +2899,7 @@
     <row r="84" spans="2:14">
       <c r="B84" s="20"/>
       <c r="C84" s="9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
@@ -2950,7 +2909,7 @@
     <row r="85" spans="2:14">
       <c r="B85" s="20"/>
       <c r="C85" s="9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
@@ -2959,60 +2918,24 @@
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C86" s="20" t="str">
-        <f>TEXT(L1,"YYYY-MM")</f>
-        <v>2025-08</v>
-      </c>
-      <c r="D86" s="8" t="str">
-        <f t="shared" ref="D86:N86" si="0">TEXT(DATE(YEAR(C86),MONTH(C86)+1,DAY(C86)),"YYYY-MM")</f>
-        <v>2025-09</v>
-      </c>
-      <c r="E86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2025-10</v>
-      </c>
-      <c r="F86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2025-11</v>
-      </c>
-      <c r="G86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2025-12</v>
-      </c>
-      <c r="H86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-01</v>
-      </c>
-      <c r="I86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-02</v>
-      </c>
-      <c r="J86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-03</v>
-      </c>
-      <c r="K86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-04</v>
-      </c>
-      <c r="L86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-05</v>
-      </c>
-      <c r="M86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-06</v>
-      </c>
-      <c r="N86" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-07</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="C86" s="20"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
@@ -3029,7 +2952,7 @@
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="20" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
@@ -3046,34 +2969,34 @@
     </row>
     <row r="90" spans="2:14">
       <c r="B90" s="14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="22" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F90" s="9"/>
       <c r="G90" s="9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="24"/>
       <c r="F91" s="68" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G91" s="54"/>
       <c r="H91" s="42"/>
@@ -3081,12 +3004,12 @@
     <row r="92" spans="2:14">
       <c r="B92" s="72"/>
       <c r="C92" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D92" s="42"/>
       <c r="E92" s="24"/>
       <c r="F92" s="68" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G92" s="54"/>
       <c r="H92" s="42"/>
@@ -3097,7 +3020,7 @@
       <c r="D93" s="73"/>
       <c r="E93" s="24"/>
       <c r="F93" s="68" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G93" s="54"/>
       <c r="H93" s="42"/>
@@ -3108,7 +3031,7 @@
       <c r="D94" s="73"/>
       <c r="E94" s="24"/>
       <c r="F94" s="68" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G94" s="54"/>
       <c r="H94" s="42"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="129">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -425,19 +425,7 @@
     <t>重要时期安全事件数</t>
   </si>
   <si>
-    <t>中秋（25/9/15-9/17）</t>
-  </si>
-  <si>
     <t>业务可用性保障</t>
-  </si>
-  <si>
-    <t>国庆（25/10/1-10/8）</t>
-  </si>
-  <si>
-    <t>元旦（26/1/1-1/3）</t>
-  </si>
-  <si>
-    <t>春节（26/2/10-2/25）</t>
   </si>
 </sst>
 </file>
@@ -2995,22 +2983,18 @@
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="24"/>
-      <c r="F91" s="68" t="s">
-        <v>128</v>
-      </c>
+      <c r="F91" s="68"/>
       <c r="G91" s="54"/>
       <c r="H91" s="42"/>
     </row>
     <row r="92" spans="2:14">
       <c r="B92" s="72"/>
       <c r="C92" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D92" s="42"/>
       <c r="E92" s="24"/>
-      <c r="F92" s="68" t="s">
-        <v>130</v>
-      </c>
+      <c r="F92" s="68"/>
       <c r="G92" s="54"/>
       <c r="H92" s="42"/>
     </row>
@@ -3019,9 +3003,7 @@
       <c r="C93" s="29"/>
       <c r="D93" s="73"/>
       <c r="E93" s="24"/>
-      <c r="F93" s="68" t="s">
-        <v>131</v>
-      </c>
+      <c r="F93" s="68"/>
       <c r="G93" s="54"/>
       <c r="H93" s="42"/>
     </row>
@@ -3030,9 +3012,7 @@
       <c r="C94" s="29"/>
       <c r="D94" s="73"/>
       <c r="E94" s="24"/>
-      <c r="F94" s="68" t="s">
-        <v>132</v>
-      </c>
+      <c r="F94" s="68"/>
       <c r="G94" s="54"/>
       <c r="H94" s="42"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="131">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -116,10 +116,16 @@
     <t>最新漏洞情报数量</t>
   </si>
   <si>
+    <t>「风险总数」</t>
+  </si>
+  <si>
     <t>最新漏洞影响资产数</t>
   </si>
   <si>
     <t>提取事件表中未公开威胁类型工单中受影响资产的IP数量</t>
+  </si>
+  <si>
+    <t>「事件总数」</t>
   </si>
   <si>
     <t>举例：护网时间</t>
@@ -1852,7 +1858,7 @@
       </c>
       <c r="I1" s="8">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -1977,9 +1983,7 @@
       <c r="C10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>6</v>
-      </c>
+      <c r="D10" s="18"/>
       <c r="E10" s="28" t="s">
         <v>23</v>
       </c>
@@ -1993,25 +1997,29 @@
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:14">
       <c r="B12" s="31"/>
       <c r="C12" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="30"/>
+        <v>27</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="20"/>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -2022,36 +2030,36 @@
       <c r="F13" s="29"/>
       <c r="G13" s="30"/>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="31"/>
       <c r="C14" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="28"/>
       <c r="F14" s="29"/>
       <c r="G14" s="30"/>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="2:14">
       <c r="B15" s="31"/>
       <c r="C15" s="27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="30"/>
@@ -2059,7 +2067,7 @@
     <row r="16" spans="2:14">
       <c r="B16" s="31"/>
       <c r="C16" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="18"/>
@@ -2069,7 +2077,7 @@
     <row r="17" spans="2:7">
       <c r="B17" s="31"/>
       <c r="C17" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="18"/>
@@ -2078,7 +2086,7 @@
     <row r="18" spans="2:7">
       <c r="B18" s="32"/>
       <c r="C18" s="27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="33"/>
@@ -2090,10 +2098,10 @@
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>6</v>
@@ -2104,10 +2112,10 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="29"/>
@@ -2117,7 +2125,7 @@
     <row r="22" spans="2:7">
       <c r="B22" s="38"/>
       <c r="C22" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>6</v>
@@ -2129,7 +2137,7 @@
     <row r="23" spans="2:7">
       <c r="B23" s="38"/>
       <c r="C23" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" s="39"/>
       <c r="E23" s="29"/>
@@ -2139,7 +2147,7 @@
     <row r="24" spans="2:7">
       <c r="B24" s="38"/>
       <c r="C24" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="29"/>
@@ -2149,7 +2157,7 @@
     <row r="25" spans="2:7">
       <c r="B25" s="40"/>
       <c r="C25" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>6</v>
@@ -2164,33 +2172,33 @@
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D27" s="13"/>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D28" s="13"/>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="38"/>
       <c r="C29" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D29" s="13"/>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="40"/>
       <c r="C30" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D30" s="42">
         <v>1</v>
@@ -2202,10 +2210,10 @@
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>6</v>
@@ -2214,7 +2222,7 @@
     <row r="33" spans="2:14">
       <c r="B33" s="38"/>
       <c r="C33" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" s="42">
         <v>1</v>
@@ -2223,42 +2231,42 @@
     <row r="34" spans="2:14">
       <c r="B34" s="38"/>
       <c r="C34" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D34" s="39"/>
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="38"/>
       <c r="C35" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" s="39"/>
     </row>
     <row r="36" spans="2:14">
       <c r="B36" s="38"/>
       <c r="C36" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D36" s="39"/>
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="38"/>
       <c r="C37" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D37" s="39"/>
     </row>
     <row r="38" spans="2:14">
       <c r="B38" s="38"/>
       <c r="C38" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D38" s="39"/>
     </row>
     <row r="39" spans="2:14">
       <c r="B39" s="40"/>
       <c r="C39" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>6</v>
@@ -2296,16 +2304,16 @@
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>21</v>
@@ -2345,15 +2353,15 @@
     </row>
     <row r="51" spans="1:14">
       <c r="B51" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C51" s="49"/>
       <c r="D51" s="20"/>
       <c r="E51" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G51" s="50"/>
       <c r="H51" s="18"/>
@@ -2370,7 +2378,7 @@
       <c r="D52" s="20"/>
       <c r="E52" s="7"/>
       <c r="F52" s="20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G52" s="50"/>
       <c r="H52" s="18"/>
@@ -2387,7 +2395,7 @@
       <c r="D53" s="20"/>
       <c r="E53" s="7"/>
       <c r="F53" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G53" s="50"/>
       <c r="H53" s="18"/>
@@ -2404,7 +2412,7 @@
       <c r="D54" s="20"/>
       <c r="E54" s="7"/>
       <c r="F54" s="20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G54" s="50"/>
       <c r="H54" s="18"/>
@@ -2421,7 +2429,7 @@
       <c r="D55" s="20"/>
       <c r="E55" s="7"/>
       <c r="F55" s="20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G55" s="50"/>
       <c r="H55" s="18"/>
@@ -2444,7 +2452,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -2461,10 +2469,10 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="8"/>
@@ -2481,7 +2489,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
@@ -2501,41 +2509,41 @@
     </row>
     <row r="61" ht="30" customHeight="1" spans="1:14">
       <c r="B61" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D61" s="54"/>
       <c r="E61" s="44"/>
       <c r="F61" s="55" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H61" s="57"/>
       <c r="I61" s="55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J61" s="56" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K61" s="57"/>
       <c r="L61" s="55" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M61" s="58" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N61" s="45"/>
     </row>
     <row r="62" ht="27" customHeight="1" spans="1:14">
       <c r="B62" s="20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D62" s="20"/>
       <c r="F62" s="59"/>
@@ -2551,7 +2559,7 @@
     <row r="63" ht="27" customHeight="1" spans="1:14">
       <c r="B63" s="20"/>
       <c r="C63" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D63" s="20"/>
       <c r="F63" s="59"/>
@@ -2567,7 +2575,7 @@
     <row r="64" ht="27" customHeight="1" spans="1:14">
       <c r="B64" s="20"/>
       <c r="C64" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D64" s="20"/>
       <c r="F64" s="59"/>
@@ -2582,10 +2590,10 @@
     </row>
     <row r="65" ht="27" customHeight="1" spans="2:14">
       <c r="B65" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>6</v>
@@ -2603,7 +2611,7 @@
     <row r="66" ht="27" customHeight="1" spans="2:14">
       <c r="B66" s="20"/>
       <c r="C66" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>6</v>
@@ -2620,10 +2628,10 @@
     </row>
     <row r="67" ht="27" customHeight="1" spans="2:14">
       <c r="B67" s="20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D67" s="20"/>
       <c r="N67" s="30"/>
@@ -2631,7 +2639,7 @@
     <row r="68" ht="27" customHeight="1" spans="2:14">
       <c r="B68" s="20"/>
       <c r="C68" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D68" s="13"/>
       <c r="N68" s="30"/>
@@ -2642,7 +2650,7 @@
     </row>
     <row r="70" spans="2:14">
       <c r="B70" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C70" s="65"/>
       <c r="D70" s="65"/>
@@ -2659,7 +2667,7 @@
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="8"/>
@@ -2676,7 +2684,7 @@
     </row>
     <row r="72" spans="2:14">
       <c r="B72" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C72" s="54"/>
       <c r="D72" s="54"/>
@@ -2693,7 +2701,7 @@
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C73" s="54"/>
       <c r="D73" s="54"/>
@@ -2710,7 +2718,7 @@
     </row>
     <row r="74" spans="2:14">
       <c r="B74" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C74" s="54"/>
       <c r="D74" s="54"/>
@@ -2727,7 +2735,7 @@
     </row>
     <row r="75" spans="2:14">
       <c r="B75" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
@@ -2744,7 +2752,7 @@
     </row>
     <row r="76" spans="2:14">
       <c r="B76" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
@@ -2761,7 +2769,7 @@
     </row>
     <row r="77" spans="2:14">
       <c r="B77" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -2781,32 +2789,32 @@
     </row>
     <row r="79" ht="28.8" spans="2:14">
       <c r="B79" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G79" s="44"/>
       <c r="H79" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K79" s="20"/>
       <c r="L79" s="44"/>
       <c r="M79" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N79" s="68" t="s">
         <v>6</v>
@@ -2816,14 +2824,14 @@
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
-      <c r="E80" s="13"/>
+      <c r="E80"/>
       <c r="F80" s="47"/>
       <c r="H80" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K80" s="20"/>
       <c r="N80" s="30"/>
@@ -2835,35 +2843,35 @@
       <c r="E81" s="29"/>
       <c r="F81" s="29"/>
       <c r="H81" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I81" s="70"/>
       <c r="J81" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K81" s="20"/>
       <c r="N81" s="30"/>
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K82" s="20"/>
       <c r="N82" s="30"/>
@@ -2871,7 +2879,7 @@
     <row r="83" spans="2:14">
       <c r="B83" s="20"/>
       <c r="C83" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
@@ -2879,7 +2887,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
       <c r="J83" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K83" s="20"/>
       <c r="N83" s="30"/>
@@ -2887,7 +2895,7 @@
     <row r="84" spans="2:14">
       <c r="B84" s="20"/>
       <c r="C84" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
@@ -2897,7 +2905,7 @@
     <row r="85" spans="2:14">
       <c r="B85" s="20"/>
       <c r="C85" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
@@ -2906,7 +2914,7 @@
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C86" s="20"/>
       <c r="D86" s="8"/>
@@ -2923,7 +2931,7 @@
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
@@ -2940,7 +2948,7 @@
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
@@ -2957,29 +2965,29 @@
     </row>
     <row r="90" spans="2:14">
       <c r="B90" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F90" s="9"/>
       <c r="G90" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="24"/>
@@ -2990,7 +2998,7 @@
     <row r="92" spans="2:14">
       <c r="B92" s="72"/>
       <c r="C92" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D92" s="42"/>
       <c r="E92" s="24"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1"/>
+    <workbookView windowWidth="27948" windowHeight="12420" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="数据统计" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="142">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -77,165 +77,201 @@
     <t>安全策略调优数量</t>
   </si>
   <si>
-    <t>外部威胁告警数量</t>
-  </si>
-  <si>
-    <t>漏洞总数量</t>
+    <t>威胁告警总</t>
+  </si>
+  <si>
+    <t>安全风险总数</t>
+  </si>
+  <si>
+    <t>核心系统威胁告警数量分布</t>
+  </si>
+  <si>
+    <t>TOP3核心资产漏洞分布</t>
+  </si>
+  <si>
+    <t>系统1</t>
   </si>
   <si>
     <t>威胁平均遏制时间</t>
   </si>
   <si>
-    <t>TOP3核心资产漏洞分布</t>
-  </si>
-  <si>
-    <t>系统1</t>
-  </si>
-  <si>
-    <t>安全事件数</t>
-  </si>
-  <si>
     <t>系统2</t>
   </si>
   <si>
+    <t>安全事件总数</t>
+  </si>
+  <si>
+    <t>系统3</t>
+  </si>
+  <si>
     <t>事件平均响应时长</t>
   </si>
   <si>
-    <t>系统3</t>
+    <t>高危可利用漏洞数</t>
+  </si>
+  <si>
+    <t>提取管理员弱口令数量</t>
+  </si>
+  <si>
+    <t>核心系统事件数量</t>
+  </si>
+  <si>
+    <t>管理员弱口令数量</t>
+  </si>
+  <si>
+    <t>最新漏洞影响资产数</t>
+  </si>
+  <si>
+    <t>提取事件表中未公开威胁类型工单中受影响资产的IP数量</t>
+  </si>
+  <si>
+    <t>「核心系统风险总数」</t>
+  </si>
+  <si>
+    <t>举例：护网时间</t>
+  </si>
+  <si>
+    <t>2026/03/01-2026/03/30</t>
+  </si>
+  <si>
+    <t>已闭环风险总数</t>
+  </si>
+  <si>
+    <t>「核心系统闭环风险数」</t>
+  </si>
+  <si>
+    <t>元旦</t>
+  </si>
+  <si>
+    <t>2026/01/01-2026/01/03</t>
+  </si>
+  <si>
+    <t>已防护漏洞数</t>
+  </si>
+  <si>
+    <t>「核心系统威胁事件总数」</t>
+  </si>
+  <si>
+    <t>春节</t>
+  </si>
+  <si>
+    <t>2026/02/15-2026/02/23</t>
+  </si>
+  <si>
+    <t>已修复漏洞数</t>
+  </si>
+  <si>
+    <t>已处置弱口令数量</t>
+  </si>
+  <si>
+    <t>业务系统数量</t>
+  </si>
+  <si>
+    <t>受影响的最新漏洞数</t>
+  </si>
+  <si>
+    <t>服务器资产数量</t>
+  </si>
+  <si>
+    <t>核心系统相关资产已闭环的风险数量分布统计</t>
+  </si>
+  <si>
+    <t>分布1</t>
+  </si>
+  <si>
+    <t>分布2</t>
+  </si>
+  <si>
+    <t>分布3</t>
+  </si>
+  <si>
+    <t>PC资产数量</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>被通报风险总数</t>
+  </si>
+  <si>
+    <t>通报风险应对</t>
+  </si>
+  <si>
+    <t>外联通报风险次数</t>
+  </si>
+  <si>
+    <t>漏扫次数</t>
+  </si>
+  <si>
+    <t>已闭环漏洞总数</t>
+  </si>
+  <si>
+    <t>已拦截外联次数</t>
+  </si>
+  <si>
+    <t>恶意外联告警数</t>
+  </si>
+  <si>
+    <t>本次汇报周期被通报次数</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>「重要时期安全日志数」</t>
+  </si>
+  <si>
+    <t>重要时期保障</t>
+  </si>
+  <si>
+    <t>「重要时期告警数」</t>
+  </si>
+  <si>
+    <t>「重要时期事件数」</t>
+  </si>
+  <si>
+    <t>「遏制率」</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>资产覆盖率</t>
+  </si>
+  <si>
+    <t>威胁遏制率</t>
+  </si>
+  <si>
+    <t>高危漏洞防护率</t>
+  </si>
+  <si>
+    <t>平均分析时间</t>
+  </si>
+  <si>
+    <t>平均响应时间</t>
+  </si>
+  <si>
+    <t>已闭环漏洞数量</t>
+  </si>
+  <si>
+    <t>威胁和事件数量</t>
+  </si>
+  <si>
+    <t>两名高级安全工程师成本</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>事件平均响应时间</t>
+  </si>
+  <si>
+    <t>事件平均处置时长</t>
   </si>
   <si>
     <t>事件闭环率</t>
   </si>
   <si>
-    <t>弱口令数量</t>
-  </si>
-  <si>
-    <t>提取管理员弱口令数量</t>
-  </si>
-  <si>
-    <t>最新漏洞情报数量</t>
-  </si>
-  <si>
-    <t>「风险总数」</t>
-  </si>
-  <si>
-    <t>最新漏洞影响资产数</t>
-  </si>
-  <si>
-    <t>提取事件表中未公开威胁类型工单中受影响资产的IP数量</t>
-  </si>
-  <si>
-    <t>「事件总数」</t>
-  </si>
-  <si>
-    <t>举例：护网时间</t>
-  </si>
-  <si>
-    <t>2026/03/01-2026/03/30</t>
-  </si>
-  <si>
-    <t>元旦</t>
-  </si>
-  <si>
-    <t>2026/01/01-2026/01/03</t>
-  </si>
-  <si>
-    <t>已闭环风险数</t>
-  </si>
-  <si>
-    <t>春节</t>
-  </si>
-  <si>
-    <t>2026/02/15-2026/02/23</t>
-  </si>
-  <si>
-    <t>受影响的最新漏洞数</t>
-  </si>
-  <si>
-    <t>已防护漏洞数</t>
-  </si>
-  <si>
-    <t>已修复漏洞数</t>
-  </si>
-  <si>
-    <t>漏洞利用攻击次数</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>前一服务周期被通报次数</t>
-  </si>
-  <si>
-    <t>通报风险应对</t>
-  </si>
-  <si>
-    <t>恶意外联次数</t>
-  </si>
-  <si>
-    <t>漏扫次数</t>
-  </si>
-  <si>
-    <t>本次汇报周期被通报次数</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>「重要时期安全日志数」</t>
-  </si>
-  <si>
-    <t>重要时期保障</t>
-  </si>
-  <si>
-    <t>「重要时期告警数」</t>
-  </si>
-  <si>
-    <t>「重要时期事件数」</t>
-  </si>
-  <si>
-    <t>「遏制率」</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>资产覆盖率</t>
-  </si>
-  <si>
-    <t>威胁遏制率</t>
-  </si>
-  <si>
-    <t>高危漏洞防护率</t>
-  </si>
-  <si>
-    <t>平均分析时间</t>
-  </si>
-  <si>
-    <t>平均响应时间</t>
-  </si>
-  <si>
-    <t>已闭环漏洞数量</t>
-  </si>
-  <si>
-    <t>威胁和事件数量</t>
-  </si>
-  <si>
-    <t>两名高级安全工程师成本</t>
-  </si>
-  <si>
-    <t>P24</t>
-  </si>
-  <si>
-    <t>安全事件总数</t>
-  </si>
-  <si>
-    <t>事件平均响应时间</t>
-  </si>
-  <si>
-    <t>事件平均处置时长</t>
-  </si>
-  <si>
     <t>安全事件类型TOP5</t>
   </si>
   <si>
@@ -342,9 +378,6 @@
   </si>
   <si>
     <t>P26</t>
-  </si>
-  <si>
-    <t>高危可利用漏洞数</t>
   </si>
   <si>
     <t>已闭环外网资产漏洞数</t>
@@ -978,7 +1011,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -987,9 +1022,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -1264,7 +1297,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1346,31 +1379,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1388,6 +1415,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1487,7 +1517,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1858,7 +1888,7 @@
       </c>
       <c r="I1" s="8">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46205</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -1924,7 +1954,7 @@
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="21"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="20"/>
@@ -1980,38 +2010,37 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:14">
       <c r="B10" s="26"/>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="18"/>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="30"/>
+      <c r="F10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="28"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="31"/>
-      <c r="C11" s="27" t="s">
-        <v>24</v>
+      <c r="B11" s="29"/>
+      <c r="C11" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D11" s="20"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="E11" s="27"/>
       <c r="G11" s="20"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:14">
-      <c r="B12" s="31"/>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="30" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="30" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="20"/>
@@ -2023,651 +2052,676 @@
       </c>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="31"/>
-      <c r="C13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="28"/>
       <c r="L13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="31"/>
-      <c r="C14" s="27" t="s">
-        <v>33</v>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="30"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="28"/>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="2:14">
-      <c r="B15" s="31"/>
-      <c r="C15" s="27" t="s">
-        <v>36</v>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="D15" s="13"/>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="31"/>
-      <c r="C16" s="27" t="s">
-        <v>37</v>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30" t="s">
+        <v>40</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="18"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="28"/>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="31"/>
-      <c r="C17" s="27" t="s">
-        <v>38</v>
+      <c r="B17" s="29"/>
+      <c r="C17" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="18"/>
-      <c r="G17" s="30"/>
+      <c r="F17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="28"/>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="32"/>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="34"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="31"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="36"/>
+      <c r="C22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="31"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="36"/>
+      <c r="C23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="31"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="36"/>
+      <c r="C24" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="36"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="38"/>
-      <c r="C22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="38"/>
-      <c r="C23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="38"/>
-      <c r="C24" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="40"/>
+      <c r="B25" s="38"/>
       <c r="C25" s="9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="36"/>
-      <c r="D26" s="41"/>
+      <c r="B26" s="34"/>
+      <c r="D26" s="40"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="37" t="s">
-        <v>46</v>
+      <c r="B27" s="35" t="s">
+        <v>58</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D27" s="13"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="38" t="s">
-        <v>48</v>
+      <c r="B28" s="36" t="s">
+        <v>60</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D28" s="13"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="38"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D29" s="13"/>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="40"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="42">
+        <v>63</v>
+      </c>
+      <c r="D30" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="36"/>
-      <c r="D31" s="41"/>
+      <c r="B31" s="34"/>
+      <c r="D31" s="40"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="37" t="s">
-        <v>52</v>
+      <c r="B32" s="35" t="s">
+        <v>64</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="2:14">
-      <c r="B33" s="38"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="42">
+        <v>66</v>
+      </c>
+      <c r="D33" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="2:14">
-      <c r="B34" s="38"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="39"/>
+        <v>67</v>
+      </c>
+      <c r="D34" s="37"/>
     </row>
     <row r="35" spans="2:14">
-      <c r="B35" s="38"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="39"/>
+        <v>68</v>
+      </c>
+      <c r="D35" s="37"/>
     </row>
     <row r="36" spans="2:14">
-      <c r="B36" s="38"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="39"/>
+        <v>69</v>
+      </c>
+      <c r="D36" s="37"/>
     </row>
     <row r="37" spans="2:14">
-      <c r="B37" s="38"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="39"/>
+        <v>70</v>
+      </c>
+      <c r="D37" s="37"/>
     </row>
     <row r="38" spans="2:14">
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="39"/>
+        <v>71</v>
+      </c>
+      <c r="D38" s="37"/>
     </row>
     <row r="39" spans="2:14">
-      <c r="B39" s="40"/>
+      <c r="B39" s="38"/>
       <c r="C39" s="9" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:14">
-      <c r="B40" s="36"/>
-      <c r="D40" s="41"/>
+      <c r="B40" s="34"/>
+      <c r="D40" s="40"/>
     </row>
     <row r="41" spans="2:14">
-      <c r="B41" s="36"/>
-      <c r="D41" s="41"/>
+      <c r="B41" s="34"/>
+      <c r="D41" s="40"/>
     </row>
     <row r="42" spans="2:14">
-      <c r="B42" s="36"/>
-      <c r="D42" s="41"/>
+      <c r="B42" s="34"/>
+      <c r="D42" s="40"/>
     </row>
     <row r="43" spans="2:14">
-      <c r="B43" s="36"/>
-      <c r="D43" s="41"/>
+      <c r="B43" s="34"/>
+      <c r="D43" s="40"/>
     </row>
     <row r="44" spans="2:14">
-      <c r="B44" s="36"/>
-      <c r="D44" s="41"/>
+      <c r="B44" s="34"/>
+      <c r="D44" s="40"/>
     </row>
     <row r="45" spans="2:14">
-      <c r="B45" s="36"/>
-      <c r="D45" s="41"/>
+      <c r="B45" s="34"/>
+      <c r="D45" s="40"/>
     </row>
     <row r="46" spans="2:14">
-      <c r="B46" s="36"/>
+      <c r="B46" s="34"/>
     </row>
     <row r="47" spans="2:14">
-      <c r="B47" s="43"/>
+      <c r="B47" s="42"/>
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="7" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48" s="44"/>
+        <v>76</v>
+      </c>
+      <c r="G48" s="43"/>
       <c r="H48" s="14"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="45"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+      <c r="N48" s="44"/>
     </row>
     <row r="49" spans="1:14">
       <c r="B49" s="7"/>
       <c r="C49" s="20"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="47"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="46"/>
       <c r="H49" s="18"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="30"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="28"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="B50" s="48"/>
+      <c r="B50" s="47"/>
       <c r="H50" s="18"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="30"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+      <c r="N50" s="28"/>
     </row>
     <row r="51" spans="1:14">
       <c r="B51" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="49"/>
+        <v>77</v>
+      </c>
+      <c r="C51" s="48"/>
       <c r="D51" s="20"/>
       <c r="E51" s="7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G51" s="50"/>
+        <v>79</v>
+      </c>
+      <c r="G51" s="49"/>
       <c r="H51" s="18"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="30"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="28"/>
     </row>
     <row r="52" spans="1:14">
       <c r="B52" s="7"/>
-      <c r="C52" s="51"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="20"/>
       <c r="E52" s="7"/>
       <c r="F52" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G52" s="50"/>
+        <v>80</v>
+      </c>
+      <c r="G52" s="49"/>
       <c r="H52" s="18"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="30"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="28"/>
     </row>
     <row r="53" spans="1:14">
       <c r="B53" s="7"/>
-      <c r="C53" s="51"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="20"/>
       <c r="E53" s="7"/>
       <c r="F53" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G53" s="50"/>
+        <v>81</v>
+      </c>
+      <c r="G53" s="49"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="30"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="28"/>
     </row>
     <row r="54" spans="1:14">
       <c r="B54" s="7"/>
-      <c r="C54" s="51"/>
+      <c r="C54" s="50"/>
       <c r="D54" s="20"/>
       <c r="E54" s="7"/>
       <c r="F54" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G54" s="50"/>
+        <v>82</v>
+      </c>
+      <c r="G54" s="49"/>
       <c r="H54" s="18"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="30"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="28"/>
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="7"/>
-      <c r="C55" s="51"/>
+      <c r="C55" s="50"/>
       <c r="D55" s="20"/>
       <c r="E55" s="7"/>
       <c r="F55" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G55" s="50"/>
+        <v>83</v>
+      </c>
+      <c r="G55" s="49"/>
       <c r="H55" s="18"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="30"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="28"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="B56" s="48"/>
+      <c r="B56" s="47"/>
       <c r="H56" s="18"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="30"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="28"/>
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="9" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
-      <c r="G57" s="52"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="34"/>
-      <c r="J57" s="34"/>
-      <c r="K57" s="34"/>
-      <c r="L57" s="34"/>
-      <c r="M57" s="34"/>
-      <c r="N57" s="35"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="39"/>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
+      <c r="N57" s="33"/>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
-      <c r="M58" s="53"/>
-      <c r="N58" s="53"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52"/>
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
-      <c r="M59" s="46"/>
-      <c r="N59" s="46"/>
+        <v>87</v>
+      </c>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="45"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
+      <c r="L59" s="45"/>
+      <c r="M59" s="45"/>
+      <c r="N59" s="45"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="B60" s="43"/>
+      <c r="B60" s="42"/>
     </row>
     <row r="61" ht="30" customHeight="1" spans="1:14">
       <c r="B61" s="20" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D61" s="54"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G61" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="H61" s="57"/>
-      <c r="I61" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="55" t="s">
-        <v>81</v>
-      </c>
-      <c r="M61" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="N61" s="45"/>
+        <v>89</v>
+      </c>
+      <c r="D61" s="53"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61" s="56"/>
+      <c r="I61" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="J61" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="K61" s="56"/>
+      <c r="L61" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="M61" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="N61" s="44"/>
     </row>
     <row r="62" ht="27" customHeight="1" spans="1:14">
       <c r="B62" s="20" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D62" s="20"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="60"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="59"/>
-      <c r="J62" s="60"/>
-      <c r="K62" s="61"/>
-      <c r="L62" s="62"/>
-      <c r="M62" s="63"/>
-      <c r="N62" s="30"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="60"/>
+      <c r="L62" s="61"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="28"/>
     </row>
     <row r="63" ht="27" customHeight="1" spans="1:14">
       <c r="B63" s="20"/>
       <c r="C63" s="9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D63" s="20"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="59"/>
-      <c r="J63" s="60"/>
-      <c r="K63" s="61"/>
-      <c r="L63" s="62"/>
-      <c r="M63" s="63"/>
-      <c r="N63" s="30"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="60"/>
+      <c r="L63" s="61"/>
+      <c r="M63" s="62"/>
+      <c r="N63" s="28"/>
     </row>
     <row r="64" ht="27" customHeight="1" spans="1:14">
       <c r="B64" s="20"/>
       <c r="C64" s="9" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D64" s="20"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="60"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="60"/>
-      <c r="K64" s="61"/>
-      <c r="L64" s="62"/>
-      <c r="M64" s="63"/>
-      <c r="N64" s="30"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="60"/>
+      <c r="L64" s="61"/>
+      <c r="M64" s="62"/>
+      <c r="N64" s="28"/>
     </row>
     <row r="65" ht="27" customHeight="1" spans="2:14">
       <c r="B65" s="20" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F65" s="59"/>
-      <c r="G65" s="60"/>
-      <c r="H65" s="61"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="56"/>
-      <c r="K65" s="61"/>
-      <c r="L65" s="62"/>
-      <c r="M65" s="63"/>
-      <c r="N65" s="30"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="61"/>
+      <c r="M65" s="62"/>
+      <c r="N65" s="28"/>
     </row>
     <row r="66" ht="27" customHeight="1" spans="2:14">
       <c r="B66" s="20"/>
       <c r="C66" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="59"/>
-      <c r="G66" s="60"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="59"/>
-      <c r="J66" s="60"/>
-      <c r="K66" s="61"/>
-      <c r="L66" s="62"/>
-      <c r="M66" s="63"/>
-      <c r="N66" s="30"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="58"/>
+      <c r="J66" s="59"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="61"/>
+      <c r="M66" s="62"/>
+      <c r="N66" s="28"/>
     </row>
     <row r="67" ht="27" customHeight="1" spans="2:14">
       <c r="B67" s="20" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D67" s="20"/>
-      <c r="N67" s="30"/>
+      <c r="N67" s="28"/>
     </row>
     <row r="68" ht="27" customHeight="1" spans="2:14">
       <c r="B68" s="20"/>
       <c r="C68" s="9" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D68" s="13"/>
-      <c r="N68" s="30"/>
+      <c r="N68" s="28"/>
     </row>
     <row r="69" spans="2:14">
       <c r="B69" s="18"/>
-      <c r="N69" s="30"/>
+      <c r="N69" s="28"/>
     </row>
     <row r="70" spans="2:14">
-      <c r="B70" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" s="65"/>
-      <c r="D70" s="65"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="65"/>
-      <c r="H70" s="65"/>
-      <c r="I70" s="65"/>
-      <c r="J70" s="65"/>
-      <c r="K70" s="65"/>
-      <c r="L70" s="65"/>
-      <c r="M70" s="65"/>
-      <c r="N70" s="66"/>
+      <c r="B70" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="64"/>
+      <c r="J70" s="64"/>
+      <c r="K70" s="64"/>
+      <c r="L70" s="64"/>
+      <c r="M70" s="64"/>
+      <c r="N70" s="65"/>
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="20" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="8"/>
@@ -2684,58 +2738,58 @@
     </row>
     <row r="72" spans="2:14">
       <c r="B72" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
-      <c r="F72" s="54"/>
-      <c r="G72" s="54"/>
-      <c r="H72" s="54"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="54"/>
-      <c r="K72" s="54"/>
-      <c r="L72" s="54"/>
-      <c r="M72" s="54"/>
-      <c r="N72" s="54"/>
+        <v>106</v>
+      </c>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53"/>
+      <c r="M72" s="53"/>
+      <c r="N72" s="53"/>
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="54"/>
-      <c r="K73" s="54"/>
-      <c r="L73" s="54"/>
-      <c r="M73" s="54"/>
-      <c r="N73" s="54"/>
+        <v>107</v>
+      </c>
+      <c r="C73" s="53"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
+      <c r="M73" s="53"/>
+      <c r="N73" s="53"/>
     </row>
     <row r="74" spans="2:14">
       <c r="B74" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="54"/>
-      <c r="G74" s="54"/>
-      <c r="H74" s="54"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="54"/>
-      <c r="K74" s="54"/>
-      <c r="L74" s="54"/>
-      <c r="M74" s="54"/>
-      <c r="N74" s="54"/>
+        <v>108</v>
+      </c>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
+      <c r="M74" s="53"/>
+      <c r="N74" s="53"/>
     </row>
     <row r="75" spans="2:14">
       <c r="B75" s="15" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
@@ -2752,7 +2806,7 @@
     </row>
     <row r="76" spans="2:14">
       <c r="B76" s="15" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
@@ -2769,7 +2823,7 @@
     </row>
     <row r="77" spans="2:14">
       <c r="B77" s="15" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -2785,38 +2839,38 @@
       <c r="N77" s="13"/>
     </row>
     <row r="78" spans="2:14">
-      <c r="C78" s="67"/>
+      <c r="C78" s="66"/>
     </row>
     <row r="79" ht="28.8" spans="2:14">
       <c r="B79" s="20" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G79" s="44"/>
+        <v>115</v>
+      </c>
+      <c r="G79" s="43"/>
       <c r="H79" s="9" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="9" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="K79" s="20"/>
-      <c r="L79" s="44"/>
+      <c r="L79" s="43"/>
       <c r="M79" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="N79" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="N79" s="67" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2824,97 +2878,96 @@
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
-      <c r="E80"/>
-      <c r="F80" s="47"/>
+      <c r="F80" s="46"/>
       <c r="H80" s="9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="9" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K80" s="20"/>
-      <c r="N80" s="30"/>
+      <c r="N80" s="28"/>
     </row>
     <row r="81" spans="2:14">
-      <c r="B81" s="69"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
       <c r="H81" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I81" s="70"/>
+        <v>121</v>
+      </c>
+      <c r="I81" s="69"/>
       <c r="J81" s="9" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K81" s="20"/>
-      <c r="N81" s="30"/>
+      <c r="N81" s="28"/>
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C82" s="71"/>
+        <v>123</v>
+      </c>
+      <c r="C82" s="70"/>
       <c r="D82" s="20" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K82" s="20"/>
-      <c r="N82" s="30"/>
+      <c r="N82" s="28"/>
     </row>
     <row r="83" spans="2:14">
       <c r="B83" s="20"/>
       <c r="C83" s="9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
-      <c r="F83" s="47"/>
+      <c r="F83" s="46"/>
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
       <c r="J83" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K83" s="20"/>
-      <c r="N83" s="30"/>
+      <c r="N83" s="28"/>
     </row>
     <row r="84" spans="2:14">
       <c r="B84" s="20"/>
       <c r="C84" s="9" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
-      <c r="F84" s="47"/>
-      <c r="N84" s="30"/>
+      <c r="F84" s="46"/>
+      <c r="N84" s="28"/>
     </row>
     <row r="85" spans="2:14">
       <c r="B85" s="20"/>
       <c r="C85" s="9" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
-      <c r="F85" s="47"/>
-      <c r="N85" s="30"/>
+      <c r="F85" s="46"/>
+      <c r="N85" s="28"/>
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="20" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C86" s="20"/>
       <c r="D86" s="8"/>
@@ -2931,7 +2984,7 @@
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="20" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
@@ -2948,7 +3001,7 @@
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="20" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
@@ -2965,91 +3018,91 @@
     </row>
     <row r="90" spans="2:14">
       <c r="B90" s="14" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="22" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F90" s="9"/>
       <c r="G90" s="9" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="12" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="24"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="54"/>
-      <c r="H91" s="42"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="41"/>
     </row>
     <row r="92" spans="2:14">
-      <c r="B92" s="72"/>
+      <c r="B92" s="71"/>
       <c r="C92" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D92" s="42"/>
+        <v>141</v>
+      </c>
+      <c r="D92" s="41"/>
       <c r="E92" s="24"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="54"/>
-      <c r="H92" s="42"/>
+      <c r="F92" s="67"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="41"/>
     </row>
     <row r="93" spans="2:14">
       <c r="B93" s="18"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="73"/>
+      <c r="C93" s="31"/>
+      <c r="D93" s="72"/>
       <c r="E93" s="24"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="54"/>
-      <c r="H93" s="42"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="53"/>
+      <c r="H93" s="41"/>
     </row>
     <row r="94" spans="2:14">
       <c r="B94" s="18"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="73"/>
+      <c r="C94" s="31"/>
+      <c r="D94" s="72"/>
       <c r="E94" s="24"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="54"/>
-      <c r="H94" s="42"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="41"/>
     </row>
     <row r="95" spans="2:14">
       <c r="B95" s="18"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="73"/>
+      <c r="C95" s="31"/>
+      <c r="D95" s="72"/>
       <c r="E95" s="24"/>
-      <c r="F95" s="68"/>
+      <c r="F95" s="67"/>
       <c r="G95" s="13"/>
-      <c r="H95" s="42"/>
+      <c r="H95" s="41"/>
     </row>
     <row r="96" spans="2:14">
       <c r="B96" s="18"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="29"/>
+      <c r="C96" s="31"/>
+      <c r="D96" s="31"/>
       <c r="E96" s="24"/>
-      <c r="F96" s="68"/>
+      <c r="F96" s="67"/>
       <c r="G96" s="13"/>
-      <c r="H96" s="42"/>
+      <c r="H96" s="41"/>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="33"/>
-      <c r="C97" s="74"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="75"/>
-      <c r="F97" s="68"/>
+      <c r="B97" s="32"/>
+      <c r="C97" s="73"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="74"/>
+      <c r="F97" s="67"/>
       <c r="G97" s="13"/>
-      <c r="H97" s="42"/>
+      <c r="H97" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="16">
